--- a/02_TRAVAIL/Lot4_ReservationsHH/MASTER_FACT_MAN_ReservationsHorsHostaway.xlsx
+++ b/02_TRAVAIL/Lot4_ReservationsHH/MASTER_FACT_MAN_ReservationsHorsHostaway.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -767,6 +767,103 @@
       <c r="A2" s="12" t="inlineStr">
         <is>
           <t>[Charge par Power Query — requete MASTER_FACT_MAN_ReservationsHorsHostaway]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RESHH-2026-05-001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CANAL_004</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DIRECT_HA_PAYANT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PROP_0003</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>LOG_0009</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>60559486</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>55</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2343.48</v>
+      </c>
+      <c r="M3" t="n">
+        <v>55</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>REF_PROPRIETAIRE</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Reservation directe Hostaway 60559486 integree (decision humaine 2026-06-15). Menage standard T3 deduit pour assiette commission.</t>
         </is>
       </c>
     </row>
